--- a/stories/arbres/ATOM-EMO.LEX.009-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.009-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Grégoire est dans la chambre avec papa. Sa sœur Hanaé a les crayons. Elle colorie un grand soleil. Grégoire la regarde longtemps. Son ventre se serre. Ses mains restent sur ses genoux. Grégoire dit : je suis jaloux. Papa écoute. Grégoire va près d'Hanaé. Il dit : je voudrais demander un tour. Hanaé dit : encore un peu. Grégoire attend la réponse. Il compte tout bas. Puis Hanaé tend un crayon. Grégoire a son tour. Il colorie un nuage. Papa dit : tu as demandé un tour. Tu as attendu. Plus tard, au salon, papa lit un livre d'images. Grégoire a encore le ventre serré. Il se souvient. Il dit : je suis jaloux. Il va demander un tour. Papa dit : encore deux pages. Grégoire attend. Puis papa ouvre le livre vers lui. Même leçon, autre moment. On nomme : jaloux. On demande un tour. On attend la réponse.</t>
+          <t>Grégoire est dans la chambre avec papa. Sa sœur Hanaé a les crayons. Elle colorie un grand soleil. Grégoire la regarde longtemps. Son ventre se serre. Ses mains restent sur ses genoux. Je suis jaloux. Papa écoute. Grégoire va près d'Hanaé. Je voudrais demander un tour. Encore un peu. Grégoire attend la réponse. Il compte tout bas. Puis Hanaé tend un crayon. Grégoire a son tour. Il colorie un nuage. Tu as demandé un tour. Tu as attendu. Plus tard, au salon, papa lit un livre d'images. Grégoire a encore le ventre serré. Il se souvient. Je suis jaloux. Il va demander un tour. Encore deux pages. Grégoire attend. Puis papa ouvre le livre vers lui. Même leçon, autre moment. On nomme : jaloux. On demande un tour. On attend la réponse.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,21 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Grégoire est dans la chambre avec papa. Sa sœur Hanaé a les crayons. Elle colorie un grand soleil. Grégoire la regarde longtemps. Son ventre se serre. Ses mains restent sur ses genoux.
+enfant-f|Je suis jaloux. Papa écoute.
+narrateur|Grégoire va près d'Hanaé.
+narrateur|Je voudrais demander un tour.
+copine|Encore un peu.
+narrateur|Grégoire attend la réponse. Il compte tout bas. Puis Hanaé tend un crayon. Grégoire a son tour. Il colorie un nuage.
+papa|Tu as demandé un tour. Tu as attendu. Plus tard, au salon, papa lit un livre d'images.
+narrateur|Grégoire a encore le ventre serré. Il se souvient.
+narrateur|Je suis jaloux. Il va demander un tour.
+papa|Encore deux pages.
+narrateur|Grégoire attend. Puis papa ouvre le livre vers lui. Même leçon, autre moment. On nomme : jaloux. On demande un tour. On attend la réponse.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1496,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Grégoire veut les crayons. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Grégoire a nommé : jaloux. Il a demandé un tour. Plus tard, avec le livre, pareil.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1832,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Grégoire range un crayon. Papa ferme le livre tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1999,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.009-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.009-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1320,6 +1325,7 @@
 narrateur|Grégoire attend. Puis papa ouvre le livre vers lui. Même leçon, autre moment. On nomme : jaloux. On demande un tour. On attend la réponse.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1503,6 +1509,7 @@
           <t>narrateur|Grégoire veut les crayons. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1681,7 @@
           <t>narrateur|Grégoire a nommé : jaloux. Il a demandé un tour. Plus tard, avec le livre, pareil.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1845,7 @@
           <t>narrateur|Grégoire range un crayon. Papa ferme le livre tout doux.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.009-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.009-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Grégoire est jaloux, il demande un tour</t>
+          <t>Les crayons de Chouchou</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nina colorie. Chouchou est jaloux. Il demande un tour. Il attend. Plus tard, avec le livre, pareil.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Grégoire est dans la chambre avec papa. Sa sœur Hanaé a les crayons. Elle colorie un grand soleil. Grégoire la regarde longtemps. Son ventre se serre. Ses mains restent sur ses genoux. Je suis jaloux. Papa écoute. Grégoire va près d'Hanaé. Je voudrais demander un tour. Encore un peu. Grégoire attend la réponse. Il compte tout bas. Puis Hanaé tend un crayon. Grégoire a son tour. Il colorie un nuage. Tu as demandé un tour. Tu as attendu. Plus tard, au salon, papa lit un livre d'images. Grégoire a encore le ventre serré. Il se souvient. Je suis jaloux. Il va demander un tour. Encore deux pages. Grégoire attend. Puis papa ouvre le livre vers lui. Même leçon, autre moment. On nomme : jaloux. On demande un tour. On attend la réponse.</t>
+          <t>Un cahier ouvert dort sur la couette. La page a un grand soleil commencé. Une boîte en métal tient les crayons. Elle fait un petit bruit, si on la touche. Une bande de soleil est sur le mur. Elle est jaune, un peu poussiéreuse. Ça sent le papier neuf. Je range les chaussettes, Chouchou. Nina a déjà le crayon jaune. La bande est chaude, papa. Oui. C'est le soleil du mur. Le cahier est bien ouvert. En ce moment, Nina colorie. Elle colorie un grand soleil. Chouchou la regarde longtemps. Son ventre se serre. Ses mains restent sur ses genoux. Je suis jaloux. Je t'écoute. Jaloux, c'est cette envie. Chouchou va près de Nina. Je voudrais demander un tour. Encore un peu. On attend la réponse. Chouchou attend. Il compte tout bas. Un. Deux. Trois. Puis Nina tend un crayon. Le bleu, pour un nuage. Merci, Nina. Chouchou a son tour. Il colorie un nuage. Tu as demandé un tour. Tu as attendu. Bravo, Chouchou. Plus tard, au salon, un livre d'images attend. Papa tient le livre sur ses genoux. Les pages sont épaisses, un peu lisses. Chouchou a encore le ventre serré. Je suis jaloux. Je voudrais demander un tour. Encore deux pages. Chouchou attend. Ses mains restent sur ses genoux. Puis papa ouvre le livre vers lui. C'est ton tour. Même leçon, autre moment. On nomme : jaloux. On demande un tour. On attend la réponse. La bande de soleil a glissé un peu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,17 +1324,57 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Grégoire est dans la chambre avec papa. Sa sœur Hanaé a les crayons. Elle colorie un grand soleil. Grégoire la regarde longtemps. Son ventre se serre. Ses mains restent sur ses genoux.
-enfant-f|Je suis jaloux. Papa écoute.
-narrateur|Grégoire va près d'Hanaé.
-narrateur|Je voudrais demander un tour.
-copine|Encore un peu.
-narrateur|Grégoire attend la réponse. Il compte tout bas. Puis Hanaé tend un crayon. Grégoire a son tour. Il colorie un nuage.
-papa|Tu as demandé un tour. Tu as attendu. Plus tard, au salon, papa lit un livre d'images.
-narrateur|Grégoire a encore le ventre serré. Il se souvient.
-narrateur|Je suis jaloux. Il va demander un tour.
+          <t>narrateur|Un cahier ouvert dort sur la couette.
+narrateur|La page a un grand soleil commencé.
+narrateur|Une boîte en métal tient les crayons.
+narrateur|Elle fait un petit bruit, si on la touche.
+narrateur|Une bande de soleil est sur le mur.
+narrateur|Elle est jaune, un peu poussiéreuse.
+narrateur|Ça sent le papier neuf.
+maman|Je range les chaussettes, Chouchou.
+papa|Nina a déjà le crayon jaune.
+enfant-m|La bande est chaude, papa.
+papa|Oui. C'est le soleil du mur.
+maman|Le cahier est bien ouvert.
+narrateur|En ce moment, Nina colorie.
+narrateur|Elle colorie un grand soleil.
+narrateur|Chouchou la regarde longtemps.
+narrateur|Son ventre se serre.
+narrateur|Ses mains restent sur ses genoux.
+enfant-m|Je suis jaloux.
+papa|Je t'écoute.
+maman|Jaloux, c'est cette envie.
+narrateur|Chouchou va près de Nina.
+enfant-m|Je voudrais demander un tour.
+enfant-f|Encore un peu.
+papa|On attend la réponse.
+narrateur|Chouchou attend.
+narrateur|Il compte tout bas.
+narrateur|Un. Deux. Trois.
+narrateur|Puis Nina tend un crayon.
+enfant-f|Le bleu, pour un nuage.
+enfant-m|Merci, Nina.
+narrateur|Chouchou a son tour.
+narrateur|Il colorie un nuage.
+papa|Tu as demandé un tour.
+papa|Tu as attendu.
+maman|Bravo, Chouchou.
+narrateur|Plus tard, au salon, un livre d'images attend.
+narrateur|Papa tient le livre sur ses genoux.
+narrateur|Les pages sont épaisses, un peu lisses.
+narrateur|Chouchou a encore le ventre serré.
+enfant-m|Je suis jaloux.
+enfant-m|Je voudrais demander un tour.
 papa|Encore deux pages.
-narrateur|Grégoire attend. Puis papa ouvre le livre vers lui. Même leçon, autre moment. On nomme : jaloux. On demande un tour. On attend la réponse.</t>
+narrateur|Chouchou attend.
+narrateur|Ses mains restent sur ses genoux.
+narrateur|Puis papa ouvre le livre vers lui.
+papa|C'est ton tour.
+maman|Même leçon, autre moment.
+enfant-m|On nomme : jaloux.
+enfant-m|On demande un tour.
+papa|On attend la réponse.
+narrateur|La bande de soleil a glissé un peu.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1350,7 +1402,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Grégoire veut les crayons. Que fait-il ?</t>
+          <t>Chouchou veut les crayons. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1427,14 +1479,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1506,7 +1558,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Grégoire veut les crayons. Que fait-il ?</t>
+          <t>narrateur|Chouchou veut les crayons.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1534,7 +1587,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Grégoire a nommé : jaloux. Il a demandé un tour. Plus tard, avec le livre, pareil.</t>
+          <t>Chouchou a nommé : jaloux. Il a demandé un tour. Plus tard, avec le livre, pareil. J'ai demandé. J'ai attendu. Oui. Les crayons, puis le livre. Bravo. C'est du bon travail. Le nuage est bleu, maintenant. Vous avez colorié ensemble. Nina a dit : encore un peu. Puis elle a tendu le crayon. On demande. On attend. La boîte en métal est refermée. Elle fait encore un petit bruit. Jaloux, on le dit. Puis on demande un tour. Le cahier reste ouvert sur la couette.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1595,14 +1648,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1678,7 +1731,22 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Grégoire a nommé : jaloux. Il a demandé un tour. Plus tard, avec le livre, pareil.</t>
+          <t>narrateur|Chouchou a nommé : jaloux.
+narrateur|Il a demandé un tour.
+narrateur|Plus tard, avec le livre, pareil.
+enfant-m|J'ai demandé. J'ai attendu.
+papa|Oui. Les crayons, puis le livre.
+maman|Bravo. C'est du bon travail.
+enfant-f|Le nuage est bleu, maintenant.
+papa|Vous avez colorié ensemble.
+enfant-m|Nina a dit : encore un peu.
+maman|Puis elle a tendu le crayon.
+papa|On demande. On attend.
+narrateur|La boîte en métal est refermée.
+narrateur|Elle fait encore un petit bruit.
+enfant-m|Jaloux, on le dit.
+maman|Puis on demande un tour.
+narrateur|Le cahier reste ouvert sur la couette.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1706,7 +1774,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Grégoire range un crayon. Papa ferme le livre tout doux.</t>
+          <t>Chouchou range un crayon. Papa ferme le livre tout doux. On pose le cahier sur la table ? Oui, maman. Merci d'avoir demandé, Chouchou. Le soleil de la page est fini. Et mon nuage, aussi. Vous avez attendu, chacun. On peut éteindre la petite lampe. Chouchou touche la couette. Elle est un peu froissée, toute douce. J'ai eu mon tour. Oui. Deux fois. Les crayons, puis le livre. La bande de soleil a presque disparu.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1767,14 +1835,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1842,7 +1910,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Grégoire range un crayon. Papa ferme le livre tout doux.</t>
+          <t>narrateur|Chouchou range un crayon.
+narrateur|Papa ferme le livre tout doux.
+maman|On pose le cahier sur la table ?
+enfant-m|Oui, maman.
+papa|Merci d'avoir demandé, Chouchou.
+enfant-f|Le soleil de la page est fini.
+enfant-m|Et mon nuage, aussi.
+maman|Vous avez attendu, chacun.
+papa|On peut éteindre la petite lampe.
+narrateur|Chouchou touche la couette.
+narrateur|Elle est un peu froissée, toute douce.
+enfant-m|J'ai eu mon tour.
+papa|Oui. Deux fois.
+maman|Les crayons, puis le livre.
+narrateur|La bande de soleil a presque disparu.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1870,7 +1952,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'étais jaloux. J'ai demandé un tour. Tu as attendu. Bravo. Le nuage est bleu. Le livre est fermé. La boîte de crayons reste calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1931,14 +2013,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2010,7 +2092,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'étais jaloux. J'ai demandé un tour.
+papa|Tu as attendu. Bravo.
+maman|Le nuage est bleu. Le livre est fermé.
+narrateur|La boîte de crayons reste calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2156,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.009-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.009-03.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Grégoire est dans la chambre avec papa. Sa sœur Hanaé a les crayons. Elle colorie un grand soleil. Grégoire la regarde longtemps. Son ventre se serre. Ses mains restent sur ses genoux. Grégoire dit : je suis &lt;emphasis level="moderate"&gt;jaloux&lt;/emphasis&gt;. Papa écoute. Grégoire va près d'Hanaé. Il dit : je voudrais demander un tour. Hanaé dit : encore un peu. Grégoire attend la réponse. Il compte tout bas. Puis Hanaé tend un crayon. Grégoire a son tour. Il colorie un nuage. Papa dit : tu as demandé un tour. Tu as attendu. Plus tard, au salon, papa lit un livre d'images. Grégoire a encore le ventre serré. Il se souvient. Il dit : je suis jaloux. Il va demander un tour. Papa dit : encore deux pages. Grégoire attend. Puis papa ouvre le livre vers lui. Même leçon, autre moment. On nomme : jaloux. On demande un tour. On attend la réponse.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un cahier ouvert dort sur la couette. La page a un grand soleil commencé. Une boîte en métal tient les crayons. Elle fait un petit bruit, si on la touche. Une bande de soleil est sur le mur. Elle est jaune, un peu poussiéreuse. Ça sent le papier neuf. Je range les chaussettes, Chouchou. Nina a déjà le crayon jaune. La bande est chaude, papa. Oui. C'est le soleil du mur. Le cahier est bien ouvert. En ce moment, Nina colorie. Elle colorie un grand soleil. Chouchou la regarde longtemps. Son ventre se serre. Ses mains restent sur ses genoux. Je suis jaloux. Je t'écoute. Jaloux, c'est cette envie. Chouchou va près de Nina. Je voudrais demander un tour. Encore un peu. On attend la réponse. Chouchou attend. Il compte tout bas. Un. Deux. Trois. Puis Nina tend un crayon. Le bleu, pour un nuage. Merci, Nina. Chouchou a son tour. Il colorie un nuage. Tu as demandé un tour. Tu as attendu. Bravo, Chouchou. Plus tard, au salon, un livre d'images attend. Papa tient le livre sur ses genoux. Les pages sont épaisses, un peu lisses. Chouchou a encore le ventre serré. Je suis jaloux. Je voudrais demander un tour. Encore deux pages. Chouchou attend. Ses mains restent sur ses genoux. Puis papa ouvre le livre vers lui. C'est ton tour. Même leçon, autre moment. On nomme : jaloux. On demande un tour. On attend la réponse. La bande de soleil a glissé un peu.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1377,7 +1377,6 @@
 narrateur|La bande de soleil a glissé un peu.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1407,7 +1406,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Grégoire veut les crayons. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou veut les crayons. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1562,7 +1561,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1587,12 +1585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Chouchou a nommé : jaloux. Il a demandé un tour. Plus tard, avec le livre, pareil. J'ai demandé. J'ai attendu. Oui. Les crayons, puis le livre. Bravo. C'est du bon travail. Le nuage est bleu, maintenant. Vous avez colorié ensemble. Nina a dit : encore un peu. Puis elle a tendu le crayon. On demande. On attend. La boîte en métal est refermée. Elle fait encore un petit bruit. Jaloux, on le dit. Puis on demande un tour. Le cahier reste ouvert sur la couette.</t>
+          <t>Chouchou a nommé : jaloux. Il a demandé un tour. Plus tard, avec le livre, pareil. J'ai demandé. J'ai attendu. Oui. Les crayons, puis le livre. Le nuage est bleu, maintenant. Vous avez colorié ensemble. Nina a dit : encore un peu. Puis elle a tendu le crayon. On demande. On attend. La boîte en métal est refermée. Elle fait encore un petit bruit. Jaloux, on le dit. Puis on demande un tour. Le cahier reste ouvert sur la couette.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Grégoire a nommé : &lt;emphasis level="moderate"&gt;jaloux&lt;/emphasis&gt;. Il a demandé un tour. Plus tard, avec le livre, pareil.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou a nommé : jaloux. Il a demandé un tour. Plus tard, avec le livre, pareil. J'ai demandé. J'ai attendu. Oui. Les crayons, puis le livre. Le nuage est bleu, maintenant. Vous avez colorié ensemble. Nina a dit : encore un peu. Puis elle a tendu le crayon. On demande. On attend. La boîte en métal est refermée. Elle fait encore un petit bruit. Jaloux, on le dit. Puis on demande un tour. Le cahier reste ouvert sur la couette.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1736,7 +1734,6 @@
 narrateur|Plus tard, avec le livre, pareil.
 enfant-m|J'ai demandé. J'ai attendu.
 papa|Oui. Les crayons, puis le livre.
-maman|Bravo. C'est du bon travail.
 enfant-f|Le nuage est bleu, maintenant.
 papa|Vous avez colorié ensemble.
 enfant-m|Nina a dit : encore un peu.
@@ -1749,7 +1746,6 @@
 narrateur|Le cahier reste ouvert sur la couette.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1779,7 +1775,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Grégoire range un crayon. Papa ferme le livre tout doux.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou range un crayon. Papa ferme le livre tout doux. On pose le cahier sur la table ? Oui, maman. Merci d'avoir demandé, Chouchou. Le soleil de la page est fini. Et mon nuage, aussi. Vous avez attendu, chacun. On peut éteindre la petite lampe. Chouchou touche la couette. Elle est un peu froissée, toute douce. J'ai eu mon tour. Oui. Deux fois. Les crayons, puis le livre. La bande de soleil a presque disparu.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1927,7 +1923,6 @@
 narrateur|La bande de soleil a presque disparu.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1952,12 +1947,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'étais jaloux. J'ai demandé un tour. Tu as attendu. Bravo. Le nuage est bleu. Le livre est fermé. La boîte de crayons reste calme. L'histoire est finie.</t>
+          <t>J'étais jaloux. J'ai demandé un tour. Tu as attendu. Bravo. Le nuage est bleu. Le livre est fermé. La boîte de crayons reste calme.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'étais jaloux. J'ai demandé un tour. Tu as attendu. Bravo. Le nuage est bleu. Le livre est fermé. La boîte de crayons reste calme.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2095,11 +2090,9 @@
           <t>enfant-m|J'étais jaloux. J'ai demandé un tour.
 papa|Tu as attendu. Bravo.
 maman|Le nuage est bleu. Le livre est fermé.
-narrateur|La boîte de crayons reste calme.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La boîte de crayons reste calme.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2118,7 +2111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2163,6 +2156,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.009-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.009-03.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Grégoire, Hanaé, papa</t>
+          <t>Chouchou, Nina, papa, maman</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.009-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.009-03.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nina colorie. Chouchou est jaloux. Il demande un tour. Il attend. Plus tard, avec le livre, pareil.</t>
+          <t>Chouchou veut colorier aussi. Nina a le crayon jaune. Chouchou dit qu'elle est jalouse, demande, attend. Au salon, elle attend le livre. Le nuage est bleu. Le livre s'ouvre vers elle.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un cahier ouvert dort sur la couette. La page a un grand soleil commencé. Une boîte en métal tient les crayons. Elle fait un petit bruit, si on la touche. Une bande de soleil est sur le mur. Elle est jaune, un peu poussiéreuse. Ça sent le papier neuf. Je range les chaussettes, Chouchou. Nina a déjà le crayon jaune. La bande est chaude, papa. Oui. C'est le soleil du mur. Le cahier est bien ouvert. En ce moment, Nina colorie. Elle colorie un grand soleil. Chouchou la regarde longtemps. Son ventre se serre. Ses mains restent sur ses genoux. Je suis jaloux. Je t'écoute. Jaloux, c'est cette envie. Chouchou va près de Nina. Je voudrais demander un tour. Encore un peu. On attend la réponse. Chouchou attend. Il compte tout bas. Un. Deux. Trois. Puis Nina tend un crayon. Le bleu, pour un nuage. Merci, Nina. Chouchou a son tour. Il colorie un nuage. Tu as demandé un tour. Tu as attendu. Bravo, Chouchou. Plus tard, au salon, un livre d'images attend. Papa tient le livre sur ses genoux. Les pages sont épaisses, un peu lisses. Chouchou a encore le ventre serré. Je suis jaloux. Je voudrais demander un tour. Encore deux pages. Chouchou attend. Ses mains restent sur ses genoux. Puis papa ouvre le livre vers lui. C'est ton tour. Même leçon, autre moment. On nomme : jaloux. On demande un tour. On attend la réponse. La bande de soleil a glissé un peu.</t>
+          <t>Un cahier ouvert dort sur la couette. La page a un grand soleil commencé. Une boîte en métal tient les crayons. Elle fait un petit bruit, si on la touche. Une bande de soleil est sur le mur. Elle est jaune, un peu poussiéreuse. Ça sent le papier neuf. Je plie les chaussettes, Chouchou. Nina a déjà le crayon jaune. La bande est chaude, papa. Oui. C'est le soleil du mur. Le cahier est bien ouvert. En ce moment, Nina colorie. Elle colorie un grand soleil. Chouchou la regarde longtemps. Son ventre se serre. Ses mains restent sur ses genoux. Je suis jalouse. Je t'écoute. Tu veux colorier aussi ? Oui. Chouchou va près de Nina. Nina, je peux après toi ? Encore un peu. On écoute Nina ? Chouchou attend. Elle compte tout bas. Un. Deux. Trois. Puis Nina tend un crayon. Le bleu, pour un nuage. Merci, Nina. Chouchou a le bleu. Elle colorie un nuage. Le nuage est joli, Chouchou. Il est pâle, encore. Plus tard, au salon, un livre d'images attend. Papa tient le livre sur ses genoux. Les pages sont épaisses, un peu lisses. Chouchou a encore le ventre serré. Papa, je voudrais voir aussi. Encore deux pages. Tu t'assoies près de moi ? Oui. Chouchou attend sur le coussin. Ses mains restent sur ses genoux. Le papier des pages sent le bois. Puis papa ouvre le livre vers elle. C'est pour toi, maintenant. Un bateau. Il a une voile blanche. Je la vois. La bande de soleil a glissé un peu. Le cahier reste ouvert, là-bas.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Un cahier ouvert dort sur la couette. La page a un grand soleil commencé. Une boîte en métal tient les crayons. Elle fait un petit bruit, si on la touche. Une bande de soleil est sur le mur. Elle est jaune, un peu poussiéreuse. Ça sent le papier neuf. Je range les chaussettes, Chouchou. Nina a déjà le crayon jaune. La bande est chaude, papa. Oui. C'est le soleil du mur. Le cahier est bien ouvert. En ce moment, Nina colorie. Elle colorie un grand soleil. Chouchou la regarde longtemps. Son ventre se serre. Ses mains restent sur ses genoux. Je suis jaloux. Je t'écoute. Jaloux, c'est cette envie. Chouchou va près de Nina. Je voudrais demander un tour. Encore un peu. On attend la réponse. Chouchou attend. Il compte tout bas. Un. Deux. Trois. Puis Nina tend un crayon. Le bleu, pour un nuage. Merci, Nina. Chouchou a son tour. Il colorie un nuage. Tu as demandé un tour. Tu as attendu. Bravo, Chouchou. Plus tard, au salon, un livre d'images attend. Papa tient le livre sur ses genoux. Les pages sont épaisses, un peu lisses. Chouchou a encore le ventre serré. Je suis jaloux. Je voudrais demander un tour. Encore deux pages. Chouchou attend. Ses mains restent sur ses genoux. Puis papa ouvre le livre vers lui. C'est ton tour. Même leçon, autre moment. On nomme : jaloux. On demande un tour. On attend la réponse. La bande de soleil a glissé un peu.</t>
+          <t>Un cahier ouvert dort sur la couette. La page a un grand soleil commencé. Une boîte en métal tient les crayons. Elle fait un petit bruit, si on la touche. Une bande de soleil est sur le mur. Elle est jaune, un peu poussiéreuse. Ça sent le papier neuf. Je plie les chaussettes, Chouchou. Nina a déjà le crayon jaune. La bande est chaude, papa. Oui. C'est le soleil du mur. Le cahier est bien ouvert. En ce moment, Nina colorie. Elle colorie un grand soleil. Chouchou la regarde longtemps. Son ventre se serre. Ses mains restent sur ses genoux. Je suis jalouse. Je t'écoute. Tu veux colorier aussi ? Oui. Chouchou va près de Nina. Nina, je peux après toi ? Encore un peu. On écoute Nina ? Chouchou attend. Elle compte tout bas. Un. Deux. Trois. Puis Nina tend un crayon. Le bleu, pour un nuage. Merci, Nina. Chouchou a le bleu. Elle colorie un nuage. Le nuage est joli, Chouchou. Il est pâle, encore. Plus tard, au salon, un livre d'images attend. Papa tient le livre sur ses genoux. Les pages sont épaisses, un peu lisses. Chouchou a encore le ventre serré. Papa, je voudrais voir aussi. Encore deux pages. Tu t'assoies près de moi ? Oui. Chouchou attend sur le coussin. Ses mains restent sur ses genoux. Le papier des pages sent le bois. Puis papa ouvre le livre vers elle. C'est pour toi, maintenant. Un bateau. Il a une voile blanche. Je la vois. La bande de soleil a glissé un peu. Le cahier reste ouvert, là-bas.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1245,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1331,50 +1331,55 @@
 narrateur|Une bande de soleil est sur le mur.
 narrateur|Elle est jaune, un peu poussiéreuse.
 narrateur|Ça sent le papier neuf.
-maman|Je range les chaussettes, Chouchou.
+maman|Je plie les chaussettes, Chouchou.
 papa|Nina a déjà le crayon jaune.
-enfant-m|La bande est chaude, papa.
-papa|Oui. C'est le soleil du mur.
+enfant-f|La bande est chaude, papa.
+papa|Oui.
+papa|C'est le soleil du mur.
 maman|Le cahier est bien ouvert.
 narrateur|En ce moment, Nina colorie.
 narrateur|Elle colorie un grand soleil.
 narrateur|Chouchou la regarde longtemps.
 narrateur|Son ventre se serre.
 narrateur|Ses mains restent sur ses genoux.
-enfant-m|Je suis jaloux.
+enfant-f|Je suis jalouse.
 papa|Je t'écoute.
-maman|Jaloux, c'est cette envie.
+papa|Tu veux colorier aussi ?
+enfant-f|Oui.
 narrateur|Chouchou va près de Nina.
-enfant-m|Je voudrais demander un tour.
+enfant-f|Nina, je peux après toi ?
 enfant-f|Encore un peu.
-papa|On attend la réponse.
+papa|On écoute Nina ?
 narrateur|Chouchou attend.
-narrateur|Il compte tout bas.
-narrateur|Un. Deux. Trois.
+narrateur|Elle compte tout bas.
+narrateur|Un.
+narrateur|Deux.
+narrateur|Trois.
 narrateur|Puis Nina tend un crayon.
 enfant-f|Le bleu, pour un nuage.
-enfant-m|Merci, Nina.
-narrateur|Chouchou a son tour.
-narrateur|Il colorie un nuage.
-papa|Tu as demandé un tour.
-papa|Tu as attendu.
-maman|Bravo, Chouchou.
+enfant-f|Merci, Nina.
+narrateur|Chouchou a le bleu.
+narrateur|Elle colorie un nuage.
+maman|Le nuage est joli, Chouchou.
+enfant-f|Il est pâle, encore.
 narrateur|Plus tard, au salon, un livre d'images attend.
 narrateur|Papa tient le livre sur ses genoux.
 narrateur|Les pages sont épaisses, un peu lisses.
 narrateur|Chouchou a encore le ventre serré.
-enfant-m|Je suis jaloux.
-enfant-m|Je voudrais demander un tour.
+enfant-f|Papa, je voudrais voir aussi.
 papa|Encore deux pages.
-narrateur|Chouchou attend.
+papa|Tu t'assoies près de moi ?
+enfant-f|Oui.
+narrateur|Chouchou attend sur le coussin.
 narrateur|Ses mains restent sur ses genoux.
-narrateur|Puis papa ouvre le livre vers lui.
-papa|C'est ton tour.
-maman|Même leçon, autre moment.
-enfant-m|On nomme : jaloux.
-enfant-m|On demande un tour.
-papa|On attend la réponse.
-narrateur|La bande de soleil a glissé un peu.</t>
+narrateur|Le papier des pages sent le bois.
+narrateur|Puis papa ouvre le livre vers elle.
+papa|C'est pour toi, maintenant.
+enfant-f|Un bateau.
+maman|Il a une voile blanche.
+enfant-f|Je la vois.
+narrateur|La bande de soleil a glissé un peu.
+narrateur|Le cahier reste ouvert, là-bas.</t>
         </is>
       </c>
     </row>
@@ -1401,12 +1406,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Chouchou veut les crayons. Que fait-il ?</t>
+          <t>Chouchou veut les crayons. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Chouchou veut les crayons. Que fait-il ?</t>
+          <t>Chouchou veut les crayons. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1421,7 +1426,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>demander un tour | un tour | jaloux | attendre | demander</t>
+          <t>demander un tour | un tour | jaloux | jalouse | attendre | demander</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1436,7 +1441,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Grégoire est jaloux. Que peut-il demander ?</t>
+          <t>Chouchou est jalouse. Que peut-elle demander ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1485,7 +1490,7 @@
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1558,7 +1563,7 @@
       <c r="AW3" t="inlineStr">
         <is>
           <t>narrateur|Chouchou veut les crayons.
-narrateur|Que fait-il ?</t>
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1585,12 +1590,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Chouchou a nommé : jaloux. Il a demandé un tour. Plus tard, avec le livre, pareil. J'ai demandé. J'ai attendu. Oui. Les crayons, puis le livre. Le nuage est bleu, maintenant. Vous avez colorié ensemble. Nina a dit : encore un peu. Puis elle a tendu le crayon. On demande. On attend. La boîte en métal est refermée. Elle fait encore un petit bruit. Jaloux, on le dit. Puis on demande un tour. Le cahier reste ouvert sur la couette.</t>
+          <t>Chouchou reprend le crayon bleu. Le nuage s'épaissit sur la page. Le jaune de Nina est fini ? Oui. Le soleil est grand. Et ton nuage, aussi. Bravo, Chouchou. La boîte en métal est refermée. Elle fait encore un petit bruit. J'ai eu le bleu. Oui. Le cahier reste ouvert sur la couette.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Chouchou a nommé : jaloux. Il a demandé un tour. Plus tard, avec le livre, pareil. J'ai demandé. J'ai attendu. Oui. Les crayons, puis le livre. Le nuage est bleu, maintenant. Vous avez colorié ensemble. Nina a dit : encore un peu. Puis elle a tendu le crayon. On demande. On attend. La boîte en métal est refermée. Elle fait encore un petit bruit. Jaloux, on le dit. Puis on demande un tour. Le cahier reste ouvert sur la couette.</t>
+          <t>Chouchou reprend le crayon bleu. Le nuage s'épaissit sur la page. Le jaune de Nina est fini ? Oui. Le soleil est grand. Et ton nuage, aussi. Bravo, Chouchou. La boîte en métal est refermée. Elle fait encore un petit bruit. J'ai eu le bleu. Oui. Le cahier reste ouvert sur la couette.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1646,14 +1651,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1729,20 +1734,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Chouchou a nommé : jaloux.
-narrateur|Il a demandé un tour.
-narrateur|Plus tard, avec le livre, pareil.
-enfant-m|J'ai demandé. J'ai attendu.
-papa|Oui. Les crayons, puis le livre.
-enfant-f|Le nuage est bleu, maintenant.
-papa|Vous avez colorié ensemble.
-enfant-m|Nina a dit : encore un peu.
-maman|Puis elle a tendu le crayon.
-papa|On demande. On attend.
+          <t>narrateur|Chouchou reprend le crayon bleu.
+narrateur|Le nuage s'épaissit sur la page.
+papa|Le jaune de Nina est fini ?
+enfant-f|Oui.
+enfant-f|Le soleil est grand.
+maman|Et ton nuage, aussi.
+papa|Bravo, Chouchou.
 narrateur|La boîte en métal est refermée.
 narrateur|Elle fait encore un petit bruit.
-enfant-m|Jaloux, on le dit.
-maman|Puis on demande un tour.
+enfant-f|J'ai eu le bleu.
+maman|Oui.
 narrateur|Le cahier reste ouvert sur la couette.</t>
         </is>
       </c>
@@ -1770,12 +1772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Chouchou range un crayon. Papa ferme le livre tout doux. On pose le cahier sur la table ? Oui, maman. Merci d'avoir demandé, Chouchou. Le soleil de la page est fini. Et mon nuage, aussi. Vous avez attendu, chacun. On peut éteindre la petite lampe. Chouchou touche la couette. Elle est un peu froissée, toute douce. J'ai eu mon tour. Oui. Deux fois. Les crayons, puis le livre. La bande de soleil a presque disparu.</t>
+          <t>Chouchou range un crayon. Papa ferme le livre tout doux. On pose le cahier sur la table ? Oui, maman. Merci d'avoir attendu, Chouchou. Le soleil de la page est fini. Et mon nuage, aussi. La voile du bateau est blanche. On peut éteindre la petite lampe ? Oui. Chouchou touche la couette. Elle est un peu froissée, toute douce. La bande de soleil a presque disparu.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Chouchou range un crayon. Papa ferme le livre tout doux. On pose le cahier sur la table ? Oui, maman. Merci d'avoir demandé, Chouchou. Le soleil de la page est fini. Et mon nuage, aussi. Vous avez attendu, chacun. On peut éteindre la petite lampe. Chouchou touche la couette. Elle est un peu froissée, toute douce. J'ai eu mon tour. Oui. Deux fois. Les crayons, puis le livre. La bande de soleil a presque disparu.</t>
+          <t>Chouchou range un crayon. Papa ferme le livre tout doux. On pose le cahier sur la table ? Oui, maman. Merci d'avoir attendu, Chouchou. Le soleil de la page est fini. Et mon nuage, aussi. La voile du bateau est blanche. On peut éteindre la petite lampe ? Oui. Chouchou touche la couette. Elle est un peu froissée, toute douce. La bande de soleil a presque disparu.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1831,14 +1833,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1909,17 +1911,15 @@
           <t>narrateur|Chouchou range un crayon.
 narrateur|Papa ferme le livre tout doux.
 maman|On pose le cahier sur la table ?
-enfant-m|Oui, maman.
-papa|Merci d'avoir demandé, Chouchou.
+enfant-f|Oui, maman.
+papa|Merci d'avoir attendu, Chouchou.
 enfant-f|Le soleil de la page est fini.
-enfant-m|Et mon nuage, aussi.
-maman|Vous avez attendu, chacun.
-papa|On peut éteindre la petite lampe.
+enfant-f|Et mon nuage, aussi.
+maman|La voile du bateau est blanche.
+papa|On peut éteindre la petite lampe ?
+enfant-f|Oui.
 narrateur|Chouchou touche la couette.
 narrateur|Elle est un peu froissée, toute douce.
-enfant-m|J'ai eu mon tour.
-papa|Oui. Deux fois.
-maman|Les crayons, puis le livre.
 narrateur|La bande de soleil a presque disparu.</t>
         </is>
       </c>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'étais jaloux. J'ai demandé un tour. Tu as attendu. Bravo. Le nuage est bleu. Le livre est fermé. La boîte de crayons reste calme.</t>
+          <t>J'ai colorié le nuage. Merci, Chouchou. Le livre reste fermé sur les genoux. La boîte de crayons reste calme.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>J'étais jaloux. J'ai demandé un tour. Tu as attendu. Bravo. Le nuage est bleu. Le livre est fermé. La boîte de crayons reste calme.</t>
+          <t>J'ai colorié le nuage. Merci, Chouchou. Le livre reste fermé sur les genoux. La boîte de crayons reste calme.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2008,14 +2008,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2087,9 +2087,9 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|J'étais jaloux. J'ai demandé un tour.
-papa|Tu as attendu. Bravo.
-maman|Le nuage est bleu. Le livre est fermé.
+          <t>enfant-f|J'ai colorié le nuage.
+papa|Merci, Chouchou.
+narrateur|Le livre reste fermé sur les genoux.
 narrateur|La boîte de crayons reste calme.</t>
         </is>
       </c>
@@ -2111,7 +2111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2161,6 +2161,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
